--- a/DateBase/orders/Dang Nguyen48_2026-10-1.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-10-1.xlsx
@@ -1223,6 +1223,9 @@
       <c r="G2" t="str">
         <v>0305101231310.5108678314812102055251010716134102010444107101220101010105154552010101010101025555510101010655510510105520101055101015575</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
